--- a/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
+++ b/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
@@ -3361,8 +3361,29 @@
       <c r="A103" t="str">
         <v>G Agraz</v>
       </c>
+      <c r="B103" t="str">
+        <v>जी अग्राज</v>
+      </c>
       <c r="C103" t="str">
         <v>2707</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Scientist-B</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Telangana</v>
+      </c>
+      <c r="F103" t="str">
+        <v>9652981749</v>
+      </c>
+      <c r="G103" t="str">
+        <v>99999</v>
+      </c>
+      <c r="H103" t="str">
+        <v>9090909090</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Telangana State Centre</v>
       </c>
     </row>
   </sheetData>

--- a/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
+++ b/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3386,9 +3386,38 @@
         <v>Telangana State Centre</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">Gopu Agraz </v>
+      </c>
+      <c r="B104" t="str">
+        <v>जी अग्राज</v>
+      </c>
+      <c r="C104" t="str">
+        <v>1999</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Scientist-E</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Telangana</v>
+      </c>
+      <c r="F104" t="str">
+        <v>9652981749</v>
+      </c>
+      <c r="G104" t="str">
+        <v>111111</v>
+      </c>
+      <c r="H104" t="str">
+        <v>9090909090</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Telangana State Centre</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
+++ b/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3415,9 +3415,17 @@
         <v>Telangana State Centre</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>ggggg</v>
+      </c>
+      <c r="C105" t="str">
+        <v>2222</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
+++ b/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I106"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3423,9 +3423,14 @@
         <v>2222</v>
       </c>
     </row>
+    <row r="106">
+      <c r="C106" t="str">
+        <v>3110</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I106"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
+++ b/rajbhasha_clone/media/data/tg_hod_officers_employee_report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3415,22 +3415,9 @@
         <v>Telangana State Centre</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>ggggg</v>
-      </c>
-      <c r="C105" t="str">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="C106" t="str">
-        <v>3110</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I106"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I104"/>
   </ignoredErrors>
 </worksheet>
 </file>